--- a/ejemplos/resultados/horario-del-grupo.xlsx
+++ b/ejemplos/resultados/horario-del-grupo.xlsx
@@ -546,15 +546,15 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -565,15 +565,15 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -584,15 +584,15 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IFERROR(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0)),"")</f>
+        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -619,7 +619,7 @@
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="37" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,7 +667,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>(clave)</t>
+          <t>(clave turno|dia)</t>
         </is>
       </c>
     </row>

--- a/ejemplos/resultados/horario-del-grupo.xlsx
+++ b/ejemplos/resultados/horario-del-grupo.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horario semanal" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casillas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asignaturas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casilla por casilla" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de la carrera" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aulas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Casillas">Casillas!$A$4:$G$12</definedName>
-    <definedName name="Asignaturas">Asignaturas!$A$4:$C$7</definedName>
-    <definedName name="Aulas">Aulas!$A$4:$A$6</definedName>
+    <definedName name="Casillas">'Casilla por casilla'!$A$4:$G$12</definedName>
+    <definedName name="Asignaturas">'Plan de la carrera'!$A$4:$C$7</definedName>
+    <definedName name="Aulas">'Aulas'!$A$4:$A$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,15 +500,15 @@
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,15 +547,15 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A4&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -565,15 +566,15 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A5&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -584,21 +585,33 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;B$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;C$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IFERROR(IF(INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))="","",INDEX(Casillas!$C$4:$C$12,MATCH($A6&amp;"|"&amp;D$3,Casillas!$H$4:$H$12,0))),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <conditionalFormatting sqref="B4:D6">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>IFERROR(INDEX('Casilla por casilla'!$I$4:$I$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),0)=3</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>IFERROR(INDEX('Casilla por casilla'!$I$4:$I$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),0)=2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>IFERROR(INDEX('Casilla por casilla'!$I$4:$I$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),0)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -607,25 +620,27 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="24" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Casillas</t>
+          <t>Casilla por casilla</t>
         </is>
       </c>
     </row>
@@ -667,6 +682,16 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>(nivel de las marcas)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>(clave turno|dia)</t>
         </is>
       </c>
@@ -693,19 +718,27 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(VLOOKUP($C4,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C4)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C4))))</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>(IFERROR(VLOOKUP($C4,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F4)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C4)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F4&amp;""),0))</f>
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>$B4&amp;"|"&amp;$A4</f>
+        <f>MID(IF(AND(NOT(($D4="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A4)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B4)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D4)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A4))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G4&amp;""),0))),IF((0-IFERROR(VALUE($G4&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G4&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G4&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G4&amp;""),0))),IF((0-IFERROR(VALUE($G4&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G4&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G4&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G4&amp;""),0))),IF((0-IFERROR(VALUE($G4&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G4&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G4&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G4&amp;""),0))),IF((0-IFERROR(VALUE($G4&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G4&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G4&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G4&amp;""),0))),IF((0-IFERROR(VALUE($G4&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G4&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G4&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C4=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>IF(OR(AND(NOT(($D4="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A4)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B4)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D4)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A4))))&gt;0))),3,IF(OR(AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0))),2,IF(OR(($C4="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J4" s="3">
+        <f>$B4&amp;CHAR(31)&amp;$A4</f>
         <v/>
       </c>
     </row>
@@ -731,19 +764,27 @@
         </is>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(VLOOKUP($C5,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C5)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C5))))</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>(IFERROR(VLOOKUP($C5,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F5)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C5)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F5&amp;""),0))</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>$B5&amp;"|"&amp;$A5</f>
+        <f>MID(IF(AND(NOT(($D5="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A5)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B5)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D5)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A5))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C5="")),(IFERROR(VALUE($G5&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G5&amp;""),0))),IF((0-IFERROR(VALUE($G5&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G5&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G5&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G5&amp;""),0))),IF((0-IFERROR(VALUE($G5&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G5&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G5&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G5&amp;""),0))),IF((0-IFERROR(VALUE($G5&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G5&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G5&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G5&amp;""),0))),IF((0-IFERROR(VALUE($G5&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G5&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G5&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G5&amp;""),0))),IF((0-IFERROR(VALUE($G5&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G5&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G5&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C5=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>IF(OR(AND(NOT(($D5="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A5)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B5)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D5)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A5))))&gt;0))),3,IF(OR(AND(NOT(($C5="")),(IFERROR(VALUE($G5&amp;""),0)&lt;0))),2,IF(OR(($C5="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="3">
+        <f>$B5&amp;CHAR(31)&amp;$A5</f>
         <v/>
       </c>
     </row>
@@ -769,19 +810,27 @@
         </is>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(VLOOKUP($C6,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C6)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C6))))</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>(IFERROR(VLOOKUP($C6,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F6)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C6)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F6&amp;""),0))</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>$B6&amp;"|"&amp;$A6</f>
+        <f>MID(IF(AND(NOT(($D6="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A6)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B6)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D6)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A6))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C6="")),(IFERROR(VALUE($G6&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G6&amp;""),0))),IF((0-IFERROR(VALUE($G6&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G6&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G6&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G6&amp;""),0))),IF((0-IFERROR(VALUE($G6&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G6&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G6&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G6&amp;""),0))),IF((0-IFERROR(VALUE($G6&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G6&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G6&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G6&amp;""),0))),IF((0-IFERROR(VALUE($G6&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G6&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G6&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G6&amp;""),0))),IF((0-IFERROR(VALUE($G6&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G6&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G6&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C6=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>IF(OR(AND(NOT(($D6="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A6)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B6)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D6)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A6))))&gt;0))),3,IF(OR(AND(NOT(($C6="")),(IFERROR(VALUE($G6&amp;""),0)&lt;0))),2,IF(OR(($C6="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>$B6&amp;CHAR(31)&amp;$A6</f>
         <v/>
       </c>
     </row>
@@ -807,19 +856,27 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(VLOOKUP($C7,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C7)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C7))))</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>(IFERROR(VLOOKUP($C7,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F7)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C7)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F7&amp;""),0))</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>$B7&amp;"|"&amp;$A7</f>
+        <f>MID(IF(AND(NOT(($D7="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A7)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B7)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D7)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A7))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C7="")),(IFERROR(VALUE($G7&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G7&amp;""),0))),IF((0-IFERROR(VALUE($G7&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G7&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G7&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G7&amp;""),0))),IF((0-IFERROR(VALUE($G7&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G7&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G7&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G7&amp;""),0))),IF((0-IFERROR(VALUE($G7&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G7&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G7&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G7&amp;""),0))),IF((0-IFERROR(VALUE($G7&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G7&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G7&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G7&amp;""),0))),IF((0-IFERROR(VALUE($G7&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G7&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G7&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C7=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
+        <f>IF(OR(AND(NOT(($D7="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A7)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B7)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D7)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A7))))&gt;0))),3,IF(OR(AND(NOT(($C7="")),(IFERROR(VALUE($G7&amp;""),0)&lt;0))),2,IF(OR(($C7="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="3">
+        <f>$B7&amp;CHAR(31)&amp;$A7</f>
         <v/>
       </c>
     </row>
@@ -845,19 +902,27 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(VLOOKUP($C8,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C8)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C8))))</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>(IFERROR(VLOOKUP($C8,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F8)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C8)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F8&amp;""),0))</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>$B8&amp;"|"&amp;$A8</f>
+        <f>MID(IF(AND(NOT(($D8="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A8)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B8)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D8)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A8))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C8="")),(IFERROR(VALUE($G8&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G8&amp;""),0))),IF((0-IFERROR(VALUE($G8&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G8&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G8&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G8&amp;""),0))),IF((0-IFERROR(VALUE($G8&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G8&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G8&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G8&amp;""),0))),IF((0-IFERROR(VALUE($G8&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G8&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G8&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G8&amp;""),0))),IF((0-IFERROR(VALUE($G8&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G8&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G8&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G8&amp;""),0))),IF((0-IFERROR(VALUE($G8&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G8&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G8&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C8=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IF(OR(AND(NOT(($D8="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A8)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B8)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D8)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A8))))&gt;0))),3,IF(OR(AND(NOT(($C8="")),(IFERROR(VALUE($G8&amp;""),0)&lt;0))),2,IF(OR(($C8="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="3">
+        <f>$B8&amp;CHAR(31)&amp;$A8</f>
         <v/>
       </c>
     </row>
@@ -883,19 +948,27 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(VLOOKUP($C9,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C9)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C9))))</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>(IFERROR(VLOOKUP($C9,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F9)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C9)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F9&amp;""),0))</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>$B9&amp;"|"&amp;$A9</f>
+        <f>MID(IF(AND(NOT(($D9="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A9)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B9)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D9)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A9))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C9="")),(IFERROR(VALUE($G9&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G9&amp;""),0))),IF((0-IFERROR(VALUE($G9&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G9&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G9&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G9&amp;""),0))),IF((0-IFERROR(VALUE($G9&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G9&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G9&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G9&amp;""),0))),IF((0-IFERROR(VALUE($G9&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G9&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G9&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G9&amp;""),0))),IF((0-IFERROR(VALUE($G9&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G9&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G9&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G9&amp;""),0))),IF((0-IFERROR(VALUE($G9&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G9&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G9&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C9=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
+        <f>IF(OR(AND(NOT(($D9="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A9)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B9)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D9)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A9))))&gt;0))),3,IF(OR(AND(NOT(($C9="")),(IFERROR(VALUE($G9&amp;""),0)&lt;0))),2,IF(OR(($C9="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="3">
+        <f>$B9&amp;CHAR(31)&amp;$A9</f>
         <v/>
       </c>
     </row>
@@ -913,19 +986,27 @@
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="3">
-        <f>IFERROR(VLOOKUP($C10,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C10)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C10))))</f>
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>(IFERROR(VLOOKUP($C10,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F10)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F10&amp;""),0))</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>$B10&amp;"|"&amp;$A10</f>
+        <f>MID(IF(AND(NOT(($D10="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A10)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B10)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D10)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A10))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C10="")),(IFERROR(VALUE($G10&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G10&amp;""),0))),IF((0-IFERROR(VALUE($G10&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G10&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G10&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G10&amp;""),0))),IF((0-IFERROR(VALUE($G10&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G10&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G10&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G10&amp;""),0))),IF((0-IFERROR(VALUE($G10&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G10&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G10&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G10&amp;""),0))),IF((0-IFERROR(VALUE($G10&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G10&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G10&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G10&amp;""),0))),IF((0-IFERROR(VALUE($G10&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G10&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G10&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C10=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
+        <f>IF(OR(AND(NOT(($D10="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A10)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B10)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D10)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A10))))&gt;0))),3,IF(OR(AND(NOT(($C10="")),(IFERROR(VALUE($G10&amp;""),0)&lt;0))),2,IF(OR(($C10="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="3">
+        <f>$B10&amp;CHAR(31)&amp;$A10</f>
         <v/>
       </c>
     </row>
@@ -951,19 +1032,27 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <f>IFERROR(VLOOKUP($C11,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F11" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C11)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C11))))</f>
         <v/>
       </c>
       <c r="G11" s="3">
-        <f>(IFERROR(VLOOKUP($C11,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F11)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C11)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F11&amp;""),0))</f>
         <v/>
       </c>
       <c r="H11" s="3">
-        <f>$B11&amp;"|"&amp;$A11</f>
+        <f>MID(IF(AND(NOT(($D11="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A11)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B11)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D11)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A11))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C11="")),(IFERROR(VALUE($G11&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G11&amp;""),0))),IF((0-IFERROR(VALUE($G11&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G11&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G11&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G11&amp;""),0))),IF((0-IFERROR(VALUE($G11&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G11&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G11&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G11&amp;""),0))),IF((0-IFERROR(VALUE($G11&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G11&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G11&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G11&amp;""),0))),IF((0-IFERROR(VALUE($G11&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G11&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G11&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G11&amp;""),0))),IF((0-IFERROR(VALUE($G11&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G11&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G11&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C11=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
+        <f>IF(OR(AND(NOT(($D11="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A11)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B11)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D11)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A11))))&gt;0))),3,IF(OR(AND(NOT(($C11="")),(IFERROR(VALUE($G11&amp;""),0)&lt;0))),2,IF(OR(($C11="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="3">
+        <f>$B11&amp;CHAR(31)&amp;$A11</f>
         <v/>
       </c>
     </row>
@@ -981,19 +1070,27 @@
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="3">
-        <f>IFERROR(VLOOKUP($C12,Asignaturas!$A$4:$C$7,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))))</f>
         <v/>
       </c>
       <c r="F12" s="3">
-        <f>COUNTIF(Casillas!$C$4:$C$12,$C12)</f>
+        <f>SUMPRODUCT(1*((EXACT('Casilla por casilla'!$C$4:$C$12,$C12))))</f>
         <v/>
       </c>
       <c r="G12" s="3">
-        <f>(IFERROR(VLOOKUP($C12,Asignaturas!$A$4:$C$7,3,FALSE),0)-$F12)</f>
+        <f>(IFERROR(VALUE(IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0)),0,IF(ISBLANK(INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))),"",INDEX('Plan de la carrera'!$C$4:$C$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))))&amp;""),0)-IFERROR(VALUE($F12&amp;""),0))</f>
         <v/>
       </c>
       <c r="H12" s="3">
-        <f>$B12&amp;"|"&amp;$A12</f>
+        <f>MID(IF(AND(NOT(($D12="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A12)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B12)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D12)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A12))))&gt;0)),"; "&amp;"Ese local esta ocupado por otro grupo a esa hora","")&amp;IF(AND(NOT(($C12="")),(IFERROR(VALUE($G12&amp;""),0)&lt;0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G12&amp;""),0))),IF((0-IFERROR(VALUE($G12&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G12&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G12&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G12&amp;""),0))),IF((0-IFERROR(VALUE($G12&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G12&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G12&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G12&amp;""),0))),IF((0-IFERROR(VALUE($G12&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G12&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G12&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G12&amp;""),0))),IF((0-IFERROR(VALUE($G12&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G12&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G12&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((0-IFERROR(VALUE($G12&amp;""),0))),IF((0-IFERROR(VALUE($G12&amp;""),0))=0,"0",ROUND((0-IFERROR(VALUE($G12&amp;""),0)),9-INT(LOG10(ABS((0-IFERROR(VALUE($G12&amp;""),0))))))&amp;""),(0-IFERROR(VALUE($G12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((0-IFERROR(VALUE($G12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(($C12=""),"; "&amp;"Turno sin asignar",""),3,32767)</f>
+        <v/>
+      </c>
+      <c r="I12" s="3">
+        <f>IF(OR(AND(NOT(($D12="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A12)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B12)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D12)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A12))))&gt;0))),3,IF(OR(AND(NOT(($C12="")),(IFERROR(VALUE($G12&amp;""),0)&lt;0))),2,IF(OR(($C12="")),1,0)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="3">
+        <f>$B12&amp;CHAR(31)&amp;$A12</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1105,7 @@
       <c r="A15" s="6" t="n"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>aula ocupada</t>
+          <t>Ese local esta ocupado por otro grupo a esa hora</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1121,7 @@
       <c r="A17" s="8" t="n"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>casilla libre</t>
+          <t>Turno sin asignar</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1129,12 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <conditionalFormatting sqref="D4:D12">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>AND(NOT(($D4="")),(SUMPRODUCT((Casillas!$D$4:$D$12=$D4)*(Casillas!$B$4:$B$12=$B4)*(Casillas!$A$4:$A$12=$A4)*(ROW(Casillas!$A$4:$A$12)&lt;&gt;ROW($A4)))&gt;0))</formula>
+      <formula>AND(NOT(($D4="")),(SUMPRODUCT(1*((EXACT('Casilla por casilla'!$A$4:$A$12,$A4)))*((EXACT('Casilla por casilla'!$B$4:$B$12,$B4)))*((EXACT('Casilla por casilla'!$D$4:$D$12,$D4)))*((ROW('Casilla por casilla'!$A$4:$A$12)&lt;&gt;ROW($A4))))&gt;0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND(NOT(($C4="")),($G4&lt;0))</formula>
+      <formula>AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="0">
       <formula>($C4="")</formula>
@@ -1045,23 +1142,24 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E12">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND(NOT(($C4="")),($G4&lt;0))</formula>
+      <formula>AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G12">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND(NOT(($C4="")),($G4&lt;0))</formula>
+      <formula>AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="C4:C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>"AL,L,IP,AM"</formula1>
+      <formula1>'Listas'!$A$4:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>"Aula 7,Aula 8,Lab 1"</formula1>
+      <formula1>'Listas'!$B$4:$B$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1070,20 +1168,20 @@
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Asignaturas</t>
+          <t>Plan de la carrera</t>
         </is>
       </c>
     </row>
@@ -1167,6 +1265,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1175,9 +1274,64 @@
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Aulas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Aula</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Aula 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Aula 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BFBFBF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1186,20 +1340,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Aulas</t>
+          <t>Listas de los desplegables</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Aula</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Aula 7</t>
         </is>
       </c>
@@ -1207,6 +1362,11 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Aula 8</t>
         </is>
       </c>
@@ -1214,7 +1374,19 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Lab 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AM</t>
         </is>
       </c>
     </row>

--- a/ejemplos/resultados/horario-del-grupo.xlsx
+++ b/ejemplos/resultados/horario-del-grupo.xlsx
@@ -498,7 +498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="008EA9DB"/>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -546,17 +546,20 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="B4" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="C4" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="D4" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
-        <v/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -565,17 +568,20 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="B5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="C5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="D5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A5&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
-        <v/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -584,18 +590,13 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="B6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;B$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="C6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;C$3)*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="D6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0)),"",IF(ISBLANK(INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0))),"",INDEX('Casilla por casilla'!$C$4:$C$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A6&amp;CHAR(31)&amp;D$3)*1,0),0))))</f>
-        <v/>
-      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -610,6 +611,11 @@
       <formula>IFERROR(INDEX('Casilla por casilla'!$I$4:$I$12,MATCH(1,INDEX(EXACT('Casilla por casilla'!$J$4:$J$12,$A4&amp;CHAR(31)&amp;B$3)*1,0),0)),0)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B4:D6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
+      <formula1>'Listas'!$A$4:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -707,10 +713,9 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
+      <c r="C4" s="3">
+        <f>IF(ISBLANK('Horario semanal'!B4),"",'Horario semanal'!B4)</f>
+        <v/>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -753,10 +758,9 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
+      <c r="C5" s="3">
+        <f>IF(ISBLANK('Horario semanal'!C4),"",'Horario semanal'!C4)</f>
+        <v/>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -799,10 +803,9 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
+      <c r="C6" s="3">
+        <f>IF(ISBLANK('Horario semanal'!D4),"",'Horario semanal'!D4)</f>
+        <v/>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -845,10 +848,9 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="C7" s="3">
+        <f>IF(ISBLANK('Horario semanal'!B5),"",'Horario semanal'!B5)</f>
+        <v/>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -891,10 +893,9 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
+      <c r="C8" s="3">
+        <f>IF(ISBLANK('Horario semanal'!C5),"",'Horario semanal'!C5)</f>
+        <v/>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -937,10 +938,9 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
+      <c r="C9" s="3">
+        <f>IF(ISBLANK('Horario semanal'!D5),"",'Horario semanal'!D5)</f>
+        <v/>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -983,7 +983,10 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="3">
+        <f>IF(ISBLANK('Horario semanal'!B6),"",'Horario semanal'!B6)</f>
+        <v/>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C10)*1,0),0))))</f>
@@ -1021,10 +1024,9 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
+      <c r="C11" s="3">
+        <f>IF(ISBLANK('Horario semanal'!C6),"",'Horario semanal'!C6)</f>
+        <v/>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -1067,7 +1069,10 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="3">
+        <f>IF(ISBLANK('Horario semanal'!D6),"",'Horario semanal'!D6)</f>
+        <v/>
+      </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0)),"",IF(ISBLANK(INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))),"",INDEX('Plan de la carrera'!$B$4:$B$7,MATCH(1,INDEX(EXACT('Plan de la carrera'!$A$4:$A$7,$C12)*1,0),0))))</f>
@@ -1150,10 +1155,7 @@
       <formula>AND(NOT(($C4="")),(IFERROR(VALUE($G4&amp;""),0)&lt;0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="C4:C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>'Listas'!$A$4:$A$7</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="D4:D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
       <formula1>'Listas'!$B$4:$B$6</formula1>
     </dataValidation>

--- a/ejemplos/resultados/horario-del-grupo.xlsx
+++ b/ejemplos/resultados/horario-del-grupo.xlsx
@@ -1118,7 +1118,7 @@
       <c r="A16" s="7" t="n"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>asignatura excedida</t>
+          <t>La asignatura tiene mas turnos que su frecuencia</t>
         </is>
       </c>
     </row>
